--- a/static/excel_files/pruebas_corr_datos_stv_evolutivo_2_perfiles.xlsx
+++ b/static/excel_files/pruebas_corr_datos_stv_evolutivo_2_perfiles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jesusalberca/Desktop/qc_matrix_generator/static/excel_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748EBC0F-4C39-3E40-AF6F-D8BC3DF28970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83EE4745-CC58-BA40-A739-D2A4CA7DED20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20540" yWindow="660" windowWidth="30500" windowHeight="20780" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -565,8 +565,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="5" width="17.6640625" customWidth="1"/>
-    <col min="6" max="6" width="68.5" customWidth="1"/>
+    <col min="3" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="73.33203125" customWidth="1"/>
+    <col min="6" max="6" width="35" customWidth="1"/>
     <col min="7" max="9" width="16.5" customWidth="1"/>
     <col min="10" max="10" width="15.5" customWidth="1"/>
     <col min="11" max="11" width="22.83203125" customWidth="1"/>
@@ -612,6 +613,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="18" customHeight="1">
+      <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
@@ -619,22 +621,23 @@
         <v>4</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="H2" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="I2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:12" ht="15">
+      <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
@@ -642,22 +645,23 @@
         <v>4</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="F3" s="4"/>
       <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="H3" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
     </row>
     <row r="4" spans="1:12" ht="30">
+      <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
@@ -665,22 +669,23 @@
         <v>4</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="H4" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="I4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" ht="30">
+      <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
@@ -688,22 +693,23 @@
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="F5" s="4"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="H5" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
     </row>
     <row r="6" spans="1:12" ht="15">
+      <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -711,22 +717,23 @@
         <v>4</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="H6" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="I6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J6" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:12" ht="30">
+      <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>3</v>
       </c>
@@ -734,22 +741,23 @@
         <v>4</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>12</v>
       </c>
+      <c r="F7" s="5"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
+      <c r="H7" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J7" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
     </row>
     <row r="8" spans="1:12" ht="30">
+      <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>3</v>
       </c>
@@ -757,22 +765,23 @@
         <v>4</v>
       </c>
       <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="F8" s="6"/>
       <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
+      <c r="H8" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="I8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J8" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" ht="15">
+      <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>3</v>
       </c>
@@ -780,22 +789,23 @@
         <v>4</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>14</v>
       </c>
+      <c r="F9" s="5"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="H9" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J9" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" ht="45">
+    <row r="10" spans="1:12" ht="30">
+      <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
         <v>3</v>
       </c>
@@ -803,22 +813,23 @@
         <v>4</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="6" t="s">
+      <c r="E10" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="F10" s="6"/>
       <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
+      <c r="H10" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="I10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J10" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" ht="15">
+      <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>3</v>
       </c>
@@ -826,22 +837,23 @@
         <v>4</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>16</v>
       </c>
+      <c r="F11" s="5"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+      <c r="H11" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J11" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
     </row>
     <row r="12" spans="1:12" ht="15">
+      <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
         <v>3</v>
       </c>
@@ -849,22 +861,23 @@
         <v>4</v>
       </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="6" t="s">
+      <c r="E12" s="6" t="s">
         <v>17</v>
       </c>
+      <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
+      <c r="H12" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="I12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J12" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" ht="30">
+      <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>3</v>
       </c>
@@ -872,22 +885,23 @@
         <v>4</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="F13" s="4"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="H13" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J13" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
     <row r="14" spans="1:12" ht="30">
+      <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
         <v>3</v>
       </c>
@@ -895,22 +909,23 @@
         <v>4</v>
       </c>
       <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="H14" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="I14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J14" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" ht="15">
+      <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
@@ -918,22 +933,23 @@
         <v>4</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="F15" s="4"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="H15" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I15" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J15" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
     </row>
     <row r="16" spans="1:12" ht="30">
+      <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
@@ -941,22 +957,23 @@
         <v>4</v>
       </c>
       <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="6" t="s">
+      <c r="E16" s="6" t="s">
         <v>12</v>
       </c>
+      <c r="F16" s="6"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
+      <c r="H16" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="I16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J16" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="2:12" ht="30">
+    <row r="17" spans="1:12" ht="30">
+      <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>3</v>
       </c>
@@ -964,22 +981,23 @@
         <v>4</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>13</v>
       </c>
+      <c r="F17" s="5"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+      <c r="H17" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J17" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="2:12" ht="15">
+    <row r="18" spans="1:12" ht="15">
+      <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>3</v>
       </c>
@@ -987,22 +1005,23 @@
         <v>4</v>
       </c>
       <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="6" t="s">
+      <c r="E18" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="F18" s="6"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
+      <c r="H18" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="I18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J18" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="2:12" ht="45">
+    <row r="19" spans="1:12" ht="30">
+      <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1010,22 +1029,23 @@
         <v>4</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>15</v>
       </c>
+      <c r="F19" s="5"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
+      <c r="H19" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I19" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J19" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="2:12" ht="15">
+    <row r="20" spans="1:12" ht="15">
+      <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
         <v>3</v>
       </c>
@@ -1033,22 +1053,22 @@
         <v>4</v>
       </c>
       <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="6" t="s">
+      <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="F20" s="6"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
+      <c r="H20" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="I20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J20" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="2:12" ht="14" hidden="1">
+    <row r="21" spans="1:12" ht="14" hidden="1">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -1061,7 +1081,7 @@
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="2:12" ht="14" hidden="1">
+    <row r="22" spans="1:12" ht="14" hidden="1">
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -1074,7 +1094,7 @@
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" spans="2:12" ht="14" hidden="1">
+    <row r="23" spans="1:12" ht="14" hidden="1">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -1087,7 +1107,7 @@
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="2:12" ht="14" hidden="1">
+    <row r="24" spans="1:12" ht="14" hidden="1">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -1100,7 +1120,7 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="2:12" ht="14" hidden="1">
+    <row r="25" spans="1:12" ht="14" hidden="1">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -1113,7 +1133,7 @@
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="2:12" ht="14" hidden="1">
+    <row r="26" spans="1:12" ht="14" hidden="1">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -1126,7 +1146,7 @@
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="2:12" ht="14" hidden="1">
+    <row r="27" spans="1:12" ht="14" hidden="1">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -1139,7 +1159,7 @@
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="2:12" ht="14" hidden="1">
+    <row r="28" spans="1:12" ht="14" hidden="1">
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -1152,7 +1172,7 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="2:12" ht="14" hidden="1">
+    <row r="29" spans="1:12" ht="14" hidden="1">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -1165,7 +1185,7 @@
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="2:12" ht="14" hidden="1">
+    <row r="30" spans="1:12" ht="14" hidden="1">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -1178,7 +1198,7 @@
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="2:12" ht="14" hidden="1">
+    <row r="31" spans="1:12" ht="14" hidden="1">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -1191,7 +1211,7 @@
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
     </row>
-    <row r="32" spans="2:12" ht="14" hidden="1">
+    <row r="32" spans="1:12" ht="14" hidden="1">
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -4611,21 +4631,21 @@
       </filters>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="J21:J290 I2:J20">
+  <conditionalFormatting sqref="J21:J290 H2:I20">
     <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Funciona">
-      <formula>NOT(ISERROR(SEARCH("Funciona",I2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Funciona",H2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Falla">
-      <formula>NOT(ISERROR(SEARCH("Falla",I2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Falla",H2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH("N/A",I2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("N/A",H2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="Pendiente">
-      <formula>NOT(ISERROR(SEARCH("Pendiente",I2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Pendiente",H2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="Por ejecutar">
-      <formula>NOT(ISERROR(SEARCH("Por ejecutar",I2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Por ejecutar",H2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
@@ -4633,16 +4653,16 @@
       <formula1>"A,B,C"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J290" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"Funciona,Falla nueva,Falla persiste,N/A,Pendiente,Por ejecutar,"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:E290" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:E290 A2:A20" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Acceso,Buscador,Control Compras,Control Parental,Navegación,NPVR,Perfiles,Rep. Canal Líneal,Reproducción,TimeShift,Transacción,Claro Música"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I20" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H20" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Bloqueante,Crítico,Mayor,Menor,"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="J21:J290 I2:I20" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"Funciona,Falla nueva,Falla persiste,N/A,Pendiente,Por ejecutar,"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
